--- a/bench-container/ig/ValueSet-careteam-roles-vs.xlsx
+++ b/bench-container/ig/ValueSet-careteam-roles-vs.xlsx
@@ -58,7 +58,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-25T14:53:07+00:00</t>
+    <t>2026-06-25T15:02:50+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
